--- a/salidas/empresas/APP.xlsx
+++ b/salidas/empresas/APP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B6" t="n">
@@ -583,7 +595,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B7" t="n">
@@ -608,7 +620,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B8" t="n">
@@ -633,7 +645,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B9" t="n">
@@ -658,7 +670,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B10" t="n">
@@ -683,7 +695,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B11" t="n">
@@ -708,7 +720,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B12" t="n">
@@ -733,7 +745,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B13" t="n">
@@ -762,7 +774,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B14" t="n">
@@ -791,7 +803,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B15" t="n">
@@ -818,7 +830,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B16" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B17" t="n">
@@ -872,7 +884,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B18" t="n">
@@ -899,7 +911,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B19" t="n">
@@ -926,7 +938,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B20" t="n">
@@ -953,7 +965,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B21" t="n">
@@ -980,7 +992,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B22" t="n">
@@ -1007,7 +1019,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B23" t="n">
@@ -1034,7 +1046,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B24" t="n">
@@ -1061,7 +1073,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B25" t="n">
@@ -1088,7 +1100,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B26" t="n">
@@ -1115,7 +1127,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B27" t="n">
@@ -1142,7 +1154,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B28" t="n">
@@ -1169,7 +1181,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B29" t="n">
@@ -1196,7 +1208,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B30" t="n">
@@ -1225,7 +1237,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B31" t="n">
@@ -1254,7 +1266,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B32" t="n">
@@ -1283,7 +1295,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B33" t="n">
@@ -1312,7 +1324,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B34" t="n">
@@ -1341,7 +1353,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B35" t="n">
@@ -1370,7 +1382,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B36" t="n">
@@ -1399,7 +1411,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B37" t="n">
@@ -1428,7 +1440,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B38" t="n">
@@ -1457,7 +1469,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B39" t="n">
@@ -1486,7 +1498,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B40" t="n">
@@ -1515,7 +1527,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B41" t="n">
@@ -1544,7 +1556,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B42" t="n">
@@ -1573,7 +1585,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B43" t="n">
@@ -1602,7 +1614,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B44" t="n">
@@ -1631,7 +1643,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B45" t="n">
@@ -1660,7 +1672,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B46" t="n">
@@ -1689,7 +1701,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B47" t="n">
@@ -1718,7 +1730,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B48" t="n">
@@ -1747,7 +1759,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B49" t="n">
@@ -1776,7 +1788,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B50" t="n">
@@ -1805,7 +1817,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B51" t="n">
@@ -1834,7 +1846,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B52" t="n">
@@ -1863,7 +1875,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B53" t="n">
@@ -1892,7 +1904,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B54" t="n">
@@ -1921,7 +1933,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B55" t="n">
@@ -1950,7 +1962,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B56" t="n">
@@ -1979,7 +1991,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B57" t="n">
@@ -2008,7 +2020,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B58" t="n">
@@ -2037,7 +2049,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B59" t="n">
@@ -2066,7 +2078,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B60" t="n">
@@ -2095,7 +2107,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B61" t="n">
@@ -2124,7 +2136,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B62" t="n">
@@ -2153,7 +2165,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B63" t="n">
@@ -2182,7 +2194,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B64" t="n">
@@ -2211,7 +2223,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B65" t="n">
@@ -2240,7 +2252,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B66" t="n">
@@ -2269,32 +2281,32 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B67" t="n">
-        <v>315.25</v>
+        <v>312.4700012207031</v>
       </c>
       <c r="C67" t="n">
-        <v>315.25</v>
+        <v>312.4700012207031</v>
       </c>
       <c r="D67" t="n">
-        <v>79284000</v>
+        <v>83251300</v>
       </c>
       <c r="E67" t="n">
         <v>13.01</v>
       </c>
       <c r="F67" t="n">
-        <v>24.23136049192929</v>
+        <v>24.0176788025137</v>
       </c>
       <c r="G67" t="n">
         <v>335291000</v>
       </c>
       <c r="H67" t="n">
-        <v>105700487750</v>
+        <v>104768379179.2908</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2364632513249685</v>
+        <v>0.2482956595912208</v>
       </c>
     </row>
   </sheetData>
@@ -2326,75 +2338,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -2430,13 +2442,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -2472,13 +2484,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -2514,13 +2526,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -2547,7 +2559,7 @@
       <c r="I5" t="n">
         <v>-0.58</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="K5" t="n">
@@ -2560,13 +2572,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -2593,7 +2605,7 @@
       <c r="I6" t="n">
         <v>-0.64</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="K6" t="n">
@@ -2606,13 +2618,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -2639,7 +2651,7 @@
       <c r="I7" t="n">
         <v>-0.5</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="K7" t="n">
@@ -2652,13 +2664,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -2685,7 +2697,7 @@
       <c r="I8" t="n">
         <v>-0.07999999999999996</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="K8" t="n">
@@ -2698,13 +2710,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -2731,7 +2743,7 @@
       <c r="I9" t="n">
         <v>0.09</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="K9" t="n">
@@ -2744,13 +2756,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -2777,7 +2789,7 @@
       <c r="I10" t="n">
         <v>-0.17</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="K10" t="n">
@@ -2790,13 +2802,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -2823,7 +2835,7 @@
       <c r="I11" t="n">
         <v>-0.27</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="K11" t="n">
@@ -2836,13 +2848,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>44875</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -2869,7 +2881,7 @@
       <c r="I12" t="n">
         <v>-0.21</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>44875</v>
       </c>
       <c r="K12" t="n">
@@ -2882,13 +2894,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -2915,7 +2927,7 @@
       <c r="I13" t="n">
         <v>-0.52</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="K13" t="n">
@@ -2928,13 +2940,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -2961,7 +2973,7 @@
       <c r="I14" t="n">
         <v>-0.22</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="K14" t="n">
@@ -2974,13 +2986,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -3007,7 +3019,7 @@
       <c r="I15" t="n">
         <v>0.05999999999999997</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="K15" t="n">
@@ -3020,13 +3032,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -3053,7 +3065,7 @@
       <c r="I16" t="n">
         <v>0.2999999999999999</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="K16" t="n">
@@ -3066,13 +3078,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -3099,7 +3111,7 @@
       <c r="I17" t="n">
         <v>0.98</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="K17" t="n">
@@ -3112,13 +3124,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -3145,7 +3157,7 @@
       <c r="I18" t="n">
         <v>1.66</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="K18" t="n">
@@ -3158,13 +3170,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -3191,7 +3203,7 @@
       <c r="I19" t="n">
         <v>2.33</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="K19" t="n">
@@ -3204,13 +3216,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -3237,7 +3249,7 @@
       <c r="I20" t="n">
         <v>3.28</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="K20" t="n">
@@ -3250,13 +3262,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -3283,7 +3295,7 @@
       <c r="I21" t="n">
         <v>4.53</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="K21" t="n">
@@ -3296,13 +3308,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -3329,7 +3341,7 @@
       <c r="I22" t="n">
         <v>5.53</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K22" t="n">
@@ -3342,13 +3354,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -3375,7 +3387,7 @@
       <c r="I23" t="n">
         <v>7.030000000000001</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="K23" t="n">
@@ -3388,13 +3400,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -3421,7 +3433,7 @@
       <c r="I24" t="n">
         <v>8.23</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K24" t="n">
@@ -3434,13 +3446,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -3467,7 +3479,7 @@
       <c r="I25" t="n">
         <v>9.75</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K25" t="n">
@@ -3480,13 +3492,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -3513,7 +3525,7 @@
       <c r="I26" t="n">
         <v>11.64</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K26" t="n">
@@ -3526,13 +3538,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -3559,7 +3571,7 @@
       <c r="I27" t="n">
         <v>13.01</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K27" t="n">
@@ -3596,52 +3608,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="C2" t="n">
@@ -3670,10 +3682,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="C3" t="n">
@@ -3702,10 +3714,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="C4" t="n">
@@ -3734,10 +3746,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="C5" t="n">
@@ -3766,10 +3778,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="C6" t="n">
@@ -3798,10 +3810,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="C7" t="n">
@@ -3830,10 +3842,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>44875</v>
       </c>
       <c r="C8" t="n">
@@ -3862,10 +3874,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="C9" t="n">
@@ -3894,10 +3906,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>45056</v>
       </c>
       <c r="C10" t="n">
@@ -3926,10 +3938,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>45147</v>
       </c>
       <c r="C11" t="n">
@@ -3958,10 +3970,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>45238</v>
       </c>
       <c r="C12" t="n">
@@ -3990,10 +4002,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>45348</v>
       </c>
       <c r="C13" t="n">
@@ -4022,10 +4034,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>45420</v>
       </c>
       <c r="C14" t="n">
@@ -4054,10 +4066,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="C15" t="n">
@@ -4086,10 +4098,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C16" t="n">
@@ -4118,10 +4130,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>45715</v>
       </c>
       <c r="C17" t="n">
@@ -4150,10 +4162,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C18" t="n">
@@ -4182,10 +4194,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C19" t="n">
@@ -4214,10 +4226,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C20" t="n">
@@ -4246,10 +4258,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C21" t="n">
@@ -4278,10 +4290,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C22" t="n">
@@ -4310,10 +4322,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C23" t="n">
@@ -4360,12 +4372,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
